--- a/photography_order_forms/033_preschool_photo_order_form--photography_order_forms.xlsx
+++ b/photography_order_forms/033_preschool_photo_order_form--photography_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'package_1',_'value':_'basic'}</t>
+          <t>package_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Package 1', 'value': 'Basic'}</t>
+          <t>Package 1</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'package_2',_'value':_'premium'}</t>
+          <t>package_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Package 2', 'value': 'Premium'}</t>
+          <t>Package 2</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'package_3',_'value':_'deluxe'}</t>
+          <t>package_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Package 3', 'value': 'Deluxe'}</t>
+          <t>Package 3</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'studio',_'value':_'studio'}</t>
+          <t>studio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Studio', 'value': 'Studio'}</t>
+          <t>Studio</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'on-location',_'value':_'on-location'}</t>
+          <t>on-location</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'On-location', 'value': 'On-location'}</t>
+          <t>On-location</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'color',_'value':_'color'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Color', 'value': 'Color'}</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'black_and_white',_'value':_'black_and_white'}</t>
+          <t>black_and_white</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Black and White', 'value': 'Black and White'}</t>
+          <t>Black and White</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'standard',_'value':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Standard', 'value': 'Standard'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'large',_'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Large', 'value': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'extra_large',_'value':_'extra_large'}</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Extra Large', 'value': 'Extra Large'}</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
